--- a/测试用例.xlsx
+++ b/测试用例.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\programming\bear\pht\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E544E48-72B2-490B-97D4-648911840074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B9F757-0ED1-4214-A67F-57C21D46EBD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="279">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -549,14 +549,6 @@
   </si>
   <si>
     <t>点击登录</t>
-  </si>
-  <si>
-    <t>1.打开页面
-2.输入账号密码验证码
-3.记住现在的验证码，点击一下验证码图片
-4.输入记住的之前的正确的验证码
-5.点击登录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>账号：admin
@@ -651,6 +643,713 @@
   </si>
   <si>
     <t>仅填写密码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>login-030</t>
+  </si>
+  <si>
+    <t>刷新页面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.打开页面
+2.刷新页面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.验证码图片更新
+2.输入框均为空
+3.验证码uuid更新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刷新页面后登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.页面正常打开
+2.存在账号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>login-031</t>
+  </si>
+  <si>
+    <t>账号：admin
+密码：admin123
+正确验证码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.打开页面
+2.输入账号密码验证码
+3.记住现在的验证码，点击一下刷新页面
+4.输入账号密码，输入记住的之前的正确的验证码
+5.点击登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.打开页面
+2.输入账号密码验证码
+3.记住现在的验证码，点击一下验证码图片
+4.输入账号密码，输入记住的之前的正确的验证码
+5.点击登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>login-032</t>
+  </si>
+  <si>
+    <t>账号：admin
+密码：admin123
+新的正确验证码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>login-033</t>
+  </si>
+  <si>
+    <t>账号：ad min
+密码：admin123
+正确验证码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.打开页面
+2.刷新页面
+3.输入账号密码验证码
+4.点击登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刷新页面后记住密码登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.打开页面
+2.输入账号密码验证码
+3.点击一下刷新页面
+4.输入账号密码，新的正确的验证码
+5.点击记住密码，登录
+6.关闭页面，再打开</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.跳转页面到若衣管理系统
+2.账号名是admin
+3.关闭页面后再打开的是若衣管理系统</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入信息后刷新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 打开登录页
+2. 输入账号、密码、验证码
+3. 点击浏览器刷新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>login-034</t>
+  </si>
+  <si>
+    <t>页面正常打开</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>页面清空验证码，并生成新的验证码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登录失败后刷新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 打开登录页
+2. 输入账号、密码、验证码
+3. 点击登录
+4.点击刷新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>login-035</t>
+  </si>
+  <si>
+    <t>页面清空所有信息，并生成新的验证码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登录成功后刷新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>login-036</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.跳转页面到若衣管理系统
+2.账号名是admin
+3.刷新后仍是若衣管理系统</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>login-037</t>
+  </si>
+  <si>
+    <t>登录成功后后退</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 打开登录页
+2. 输入账号、密码、验证码
+3. 点击登录
+4.点击后退</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.跳转页面到若衣管理系统
+2.账号名是admin
+3.后退后仍然是若依管理系统页面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登录页面返回后前进</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>login-038</t>
+  </si>
+  <si>
+    <t>login-039</t>
+  </si>
+  <si>
+    <t>login-040</t>
+  </si>
+  <si>
+    <t>登录页面返回后前进，再登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 打开登录页
+2.点击后退
+3.点击前进
+4. 输入账号、密码、验证码登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.跳转页面到若衣管理系统
+2.账号名是admin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登录页面返回后前进，再登录输入不正确账号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.页面正常打开
+2.存在账号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.打开页面
+2.返回
+3.前进</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登录成功两次，注销登录一次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>login-041</t>
+  </si>
+  <si>
+    <t>1.打开页面
+2.输入账号密码验证码
+3.点击登录
+4.再创建个新页面重复一次登录
+5.再在新页面注销登录
+6.刷新两个页面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>两个页面刷新后返回登录页面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户管理-新增</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户管理-修改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户管理-删除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>add-001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户昵称:普通人ptr
+用户名称:ptr123
+用户密码:123456</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只填必填项</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有信息全填</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>add-002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.使用admin账号
+2.页面正常打开
+3.状态正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.使用admin账号
+2.页面正常打开
+3.状态停用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只填必填项，但停用账号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只填必填项，点击取消</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击添加用户，刷新页面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加正常状态用户后账号可正常登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加停用状态用户后账号无法登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加正常状态用户显示信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快速连续点击两次确定仅添加一条用户</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加用户成功后点击新增按钮弹窗内容清空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同一用户名称重复添加提示已存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除指定用户不能登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除指定用户有弹窗提示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除admin用户</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除指定common用户</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改指定用户，只填必填值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改指定用户，界面生效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改指定用户界面，点击取消</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改正常状态用户后账号可正常登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改停用状态用户后账号无法登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改指定用户，指定部门</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>add-003</t>
+  </si>
+  <si>
+    <t>add-004</t>
+  </si>
+  <si>
+    <t>add-005</t>
+  </si>
+  <si>
+    <t>add-006</t>
+  </si>
+  <si>
+    <t>add-007</t>
+  </si>
+  <si>
+    <t>add-008</t>
+  </si>
+  <si>
+    <t>add-009</t>
+  </si>
+  <si>
+    <t>add-010</t>
+  </si>
+  <si>
+    <t>add-011</t>
+  </si>
+  <si>
+    <t>alter-001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alter-002</t>
+  </si>
+  <si>
+    <t>alter-003</t>
+  </si>
+  <si>
+    <t>alter-004</t>
+  </si>
+  <si>
+    <t>alter-005</t>
+  </si>
+  <si>
+    <t>alter-006</t>
+  </si>
+  <si>
+    <t>del-001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>del-002</t>
+  </si>
+  <si>
+    <t>del-003</t>
+  </si>
+  <si>
+    <t>del-004</t>
+  </si>
+  <si>
+    <t>用户昵称:普通人ptr
+归属部门：深圳总公司测试部门
+手机号码：符合格式的号码
+邮箱：符合格式的邮箱
+性别：女
+岗位：普通员工
+角色：普通角色
+用户名称:ptr123
+用户密码:123456
+备注：123</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.使用admin账号
+2.页面正常打开
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户昵称:普通人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户名称:ptr123
+用户密码:123456</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>归属部门：深圳总公司测试部门</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.登录到首页
+2.进入到用户管理，点击新增
+3.填入昵称，名称，密码
+4.点击确定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ry数据库user表多了ptr123用户
+网页端表格多了普通人ptr用户</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.登录到首页
+2.进入到用户管理，点击新增
+3.填入全部信息
+4.点击确定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ry数据库user表多了ptr123用户
+网页端表格多了普通人ptr用户，信息完全</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ry数据库user表多了ptr123用户
+网页端表格多了普通人ptr用户，显示停用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.使用admin账号
+2.页面正常打开</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.登录到首页
+2.进入到用户管理
+3.点击新增，填入必填项，勾选停用账号
+4.点击确定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.登录到首页
+2.进入到用户管理
+3.点击新增，填入必填项
+4.点击取消</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ry数据库user表没有新增用户
+网页端表格没有新增用户</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户昵称:普通人ptr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.登录到首页
+2.进入到用户管理
+3.点击新增，输入用户昵称普通人ptr
+4.刷新页面
+5.点击新增</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增页面不保存数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.使用admin账号
+2.页面正常打开
+3.之前不存在普通人ptr用户</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.登录到首页
+2.进入到用户管理，点击新增
+3.填入昵称，名称，密码
+4.点击确定
+5.注销登录
+6.输入名称和密码
+7.点击登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提示账户已封禁，请联系管理员</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格显示添加用户的信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.登录到首页
+2.进入到用户管理，点击新增
+3.填入昵称，名称，密码
+4.点击两次确定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ry数据库user表多了一个ptr123用户
+网页端表格多了一个普通人ptr用户</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.登录到首页
+2.进入到用户管理，点击新增
+3.填入昵称，名称，密码
+4.点击确定
+5.再次点击新增按钮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增所有行都为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.登录到首页
+2.进入到用户管理，点击新增
+3.填入昵称，名称，密码
+4.点击确定
+5.再重复上述添加操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提示已存在，查询ry只有一条数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.使用admin账号
+2.页面正常打开
+3.存在普通人ptr用户</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ry数据库user表ptr123用户的昵称变为普通人
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.登录到首页
+2.进入到用户管理，点击普通人ptr用户的选择框
+3.点击修改
+4.修改用户昵称，确定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网页端界面普通人ptr变成普通人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.登录到首页
+2.进入到用户管理，点击普通人ptr用户的选择框
+3.点击修改
+4.点击取消</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网页端界面普通人ptr无变化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.登录到首页
+2.进入到用户管理，点击普通人ptr用户的选择框
+3.点击修改
+4.修改为停用，确定
+5.注销登录
+6.输入名称和密码
+7.点击登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.跳转页面到若衣管理系统
+2.弹出需要修改密码
+3.账号名是普通人ptr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.登录到首页
+2.进入到用户管理，点击普通人ptr用户的选择框
+3.点击修改
+4.修改为正常，确定
+5.注销登录
+6.输入名称和密码
+7.点击登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.跳转页面到若衣管理系统
+2.弹出需要修改密码
+3.账号名是普通人ptr
+4.修改表格显示为正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提示账户已封禁，请联系管理员
+修改表格显示为停用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.登录到首页
+2.进入到用户管理，点击普通人ptr用户的选择框
+3.点击修改
+4.指定相应部门，确定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网页端显示部门下有该用户
+数据库查询该用户有对应depid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.登录到首页
+2.进入到用户管理，点击普通人ptr用户的选择框
+3.点击删除，再确定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库查询该用户被删除
+表格消失显示该用户</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.登录到首页
+2.进入到用户管理，点击普通人ptr用户的选择框
+3.点击删除，再确定
+4.注销登录
+5.输入名称和密码
+6.点击登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提示用户名不存在/密码错误</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有提示框让你再次确定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.登录到首页
+2.进入到用户管理，点击admin用户的选择框
+3.点击删除，再确定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提示无权限删除</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -694,7 +1393,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -704,6 +1403,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -985,7 +1687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1092,7 +1794,7 @@
         <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>22</v>
@@ -1192,7 +1894,7 @@
         <v>41</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>94</v>
@@ -1217,7 +1919,7 @@
         <v>42</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>95</v>
@@ -1267,7 +1969,7 @@
         <v>64</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>26</v>
@@ -1342,7 +2044,7 @@
         <v>67</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>98</v>
@@ -1367,7 +2069,7 @@
         <v>68</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>99</v>
@@ -1392,7 +2094,7 @@
         <v>69</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>100</v>
@@ -1417,7 +2119,7 @@
         <v>70</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>101</v>
@@ -1442,13 +2144,13 @@
         <v>71</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>102</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>38</v>
@@ -1461,7 +2163,7 @@
         <v>8</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>72</v>
@@ -1486,7 +2188,7 @@
         <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>73</v>
@@ -1580,7 +2282,7 @@
       </c>
       <c r="I23" s="2"/>
     </row>
-    <row r="24" spans="1:9" ht="84" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="98" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2" t="s">
         <v>8</v>
@@ -1595,10 +2297,10 @@
         <v>21</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>38</v>
@@ -1623,10 +2325,10 @@
         <v>14</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I25" s="2"/>
     </row>
@@ -1648,10 +2350,10 @@
         <v>14</v>
       </c>
       <c r="G26" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="I26" s="2"/>
     </row>
@@ -1667,13 +2369,13 @@
         <v>80</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="F27" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>16</v>
@@ -1698,10 +2400,10 @@
         <v>110</v>
       </c>
       <c r="G28" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="I28" s="2"/>
     </row>
@@ -1717,16 +2419,16 @@
         <v>82</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="56" x14ac:dyDescent="0.3">
@@ -1735,399 +2437,845 @@
         <v>8</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>83</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I30" s="2"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="42" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
+      <c r="B31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>136</v>
+      </c>
       <c r="I31" s="2"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="98" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
+      <c r="B32" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="I32" s="2"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="98" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
+      <c r="B33" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>151</v>
+      </c>
       <c r="I33" s="2"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
+      <c r="B34" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="I34" s="2"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="42" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
+      <c r="B35" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>156</v>
+      </c>
       <c r="I35" s="2"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
+      <c r="B36" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>160</v>
+      </c>
       <c r="I36" s="2"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
+      <c r="B37" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>163</v>
+      </c>
       <c r="I37" s="2"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
+      <c r="B38" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>167</v>
+      </c>
       <c r="I38" s="2"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
+      <c r="B39" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>174</v>
+      </c>
       <c r="I39" s="2"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
+      <c r="B40" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>275</v>
+      </c>
       <c r="I40" s="2"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" ht="42" x14ac:dyDescent="0.3">
       <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
+      <c r="B41" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>136</v>
+      </c>
       <c r="I41" s="2"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="84" x14ac:dyDescent="0.3">
       <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
+      <c r="B42" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>183</v>
+      </c>
       <c r="I42" s="2"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
+      <c r="B43" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>238</v>
+      </c>
       <c r="I43" s="2"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" ht="168" x14ac:dyDescent="0.3">
       <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
+      <c r="B44" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>240</v>
+      </c>
       <c r="I44" s="2"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="70" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
+      <c r="B45" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>241</v>
+      </c>
       <c r="I45" s="2"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
+      <c r="B46" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>245</v>
+      </c>
       <c r="I46" s="2"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="84" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
+      <c r="B47" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>248</v>
+      </c>
       <c r="I47" s="2"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="98" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
+      <c r="B48" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>266</v>
+      </c>
       <c r="I48" s="2"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" ht="98" x14ac:dyDescent="0.3">
       <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
+      <c r="B49" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="I49" s="2"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
+      <c r="B50" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>252</v>
+      </c>
       <c r="I50" s="2"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
+      <c r="B51" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>254</v>
+      </c>
       <c r="I51" s="2"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" ht="70" x14ac:dyDescent="0.3">
       <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
+      <c r="B52" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>256</v>
+      </c>
       <c r="I52" s="2"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" ht="70" x14ac:dyDescent="0.3">
       <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
+      <c r="B53" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>258</v>
+      </c>
       <c r="I53" s="2"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" ht="70" x14ac:dyDescent="0.3">
       <c r="A54" s="2"/>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
+      <c r="B54" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>260</v>
+      </c>
       <c r="I54" s="2"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" ht="70" x14ac:dyDescent="0.3">
       <c r="A55" s="2"/>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
+      <c r="B55" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>262</v>
+      </c>
       <c r="I55" s="2"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" ht="70" x14ac:dyDescent="0.3">
       <c r="A56" s="2"/>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
+      <c r="B56" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>264</v>
+      </c>
       <c r="I56" s="2"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" ht="112" x14ac:dyDescent="0.3">
       <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
+      <c r="B57" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>268</v>
+      </c>
       <c r="I57" s="2"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" ht="112" x14ac:dyDescent="0.3">
       <c r="A58" s="2"/>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
+      <c r="B58" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>269</v>
+      </c>
       <c r="I58" s="2"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="2"/>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="2"/>
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="2"/>
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="1"/>
-      <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63" s="1"/>
-      <c r="B63" s="1"/>
-      <c r="C63" s="1"/>
-      <c r="D63" s="1"/>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" s="1"/>
-      <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
+    <row r="59" spans="1:9" ht="70" x14ac:dyDescent="0.3">
+      <c r="A59" s="1"/>
+      <c r="B59" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="I59" s="1"/>
+    </row>
+    <row r="60" spans="1:9" ht="56" x14ac:dyDescent="0.3">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="I60" s="1"/>
+    </row>
+    <row r="61" spans="1:9" ht="98" x14ac:dyDescent="0.3">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I61" s="1"/>
+    </row>
+    <row r="62" spans="1:9" ht="56" x14ac:dyDescent="0.3">
+      <c r="B62" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="56" x14ac:dyDescent="0.3">
+      <c r="B63" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>278</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/测试用例.xlsx
+++ b/测试用例.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\programming\bear\pht\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B9F757-0ED1-4214-A67F-57C21D46EBD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E9AA73A-FC2B-4C0A-B5AF-72A6C7A158A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="279">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -139,12 +139,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>账号：ad min
-密码：admin123
-正确验证码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>提示用户名不存在/密码错误</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -153,18 +147,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>账号：
-密码：admin123
-正确验证码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>账号：admin
-密码：admin 123
-正确验证码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>login-005</t>
   </si>
   <si>
@@ -177,24 +159,6 @@
   </si>
   <si>
     <t>login-006</t>
-  </si>
-  <si>
-    <t>账号：admin
-密码：
-正确验证码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.打开页面
-2.输入密码验证码
-3.点击登录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.打开页面
-2.输入账号验证码
-3.点击登录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>验证码包含空格</t>
@@ -383,19 +347,7 @@
     <t>login-029</t>
   </si>
   <si>
-    <t>账号：admin
-密码：admin123
-正确验证码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>优先级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>账号：admin@a
-密码：admin123
-正确验证码</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -415,35 +367,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>账号：admin
-密码：adm是in123
-正确验证码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>密码限制非英文数字符号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1.打开页面
-2.键盘尝试输入账号密码
-3.用复制粘贴常熟输入密码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>密码框无法输入非英文数字符号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>账号：admin
-密码： admin123 
-正确验证码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>账号：admin
-密码：Admin123
-正确验证码</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -616,23 +544,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1.打开页面
-2.输入账号密码验证码，登录
-3.点击头像
-4.点击退出，并点确认
-5.输入账号密码验证码，登录
-6.点击头像
-7.点击退出，并点确认</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.打开页面
-2.输入账号密码验证码
-3.登录，关闭页面
-4.打开页面</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1.页面正常打开
 2.系统中已存在合法账号admin，对应为admin123</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -678,20 +589,6 @@
   </si>
   <si>
     <t>login-031</t>
-  </si>
-  <si>
-    <t>账号：admin
-密码：admin123
-正确验证码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.打开页面
-2.输入账号密码验证码
-3.记住现在的验证码，点击一下刷新页面
-4.输入账号密码，输入记住的之前的正确的验证码
-5.点击登录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1.打开页面
@@ -714,29 +611,7 @@
     <t>login-033</t>
   </si>
   <si>
-    <t>账号：ad min
-密码：admin123
-正确验证码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.打开页面
-2.刷新页面
-3.输入账号密码验证码
-4.点击登录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>刷新页面后记住密码登录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.打开页面
-2.输入账号密码验证码
-3.点击一下刷新页面
-4.输入账号密码，新的正确的验证码
-5.点击记住密码，登录
-6.关闭页面，再打开</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -771,18 +646,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1. 打开登录页
-2. 输入账号、密码、验证码
-3. 点击登录
-4.点击刷新</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>login-035</t>
-  </si>
-  <si>
-    <t>页面清空所有信息，并生成新的验证码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>登录成功后刷新</t>
@@ -806,13 +670,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1. 打开登录页
-2. 输入账号、密码、验证码
-3. 点击登录
-4.点击后退</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1.跳转页面到若衣管理系统
 2.账号名是admin
 3.后退后仍然是若依管理系统页面</t>
@@ -836,13 +693,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1. 打开登录页
-2.点击后退
-3.点击前进
-4. 输入账号、密码、验证码登录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1.跳转页面到若衣管理系统
 2.账号名是admin</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -875,15 +725,6 @@
   </si>
   <si>
     <t>login-041</t>
-  </si>
-  <si>
-    <t>1.打开页面
-2.输入账号密码验证码
-3.点击登录
-4.再创建个新页面重复一次登录
-5.再在新页面注销登录
-6.刷新两个页面</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>两个页面刷新后返回登录页面</t>
@@ -1351,6 +1192,155 @@
   <si>
     <t>提示无权限删除</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">账号：ad min
+密码：admin123
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">账号：
+密码：admin123
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">账号：admin@a
+密码：admin123
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">账号：admin
+密码：adm是in123
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.打开页面
+2.键盘尝试输入账号密码
+3.用复制粘贴输入密码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">账号：admin
+密码： admin123 
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">账号：admin
+密码：Admin123
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">账号：admin
+密码：
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">账号：admin
+密码：admin 123
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">账号：admin
+密码：admin123
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.打开页面
+2.输入账号密码，登录
+3.点击头像
+4.点击退出，并点确认
+5.输入账号密码，登录
+6.点击头像
+7.点击退出，并点确认</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.打开页面
+2.输入账号密码
+3.登录，关闭页面
+4.打开页面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.打开页面
+2.刷新页面
+3.输入账号密码
+4.点击登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.打开页面
+2.点击一下刷新页面
+3.输入账号密码，新的正确的验证码
+4.点击记住密码，登录
+5.关闭页面，再打开</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.打开页面
+2.记住现在的验证码，点击一下刷新页面
+3.输入账号密码，输入记住的之前的正确的验证码
+4.点击登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 打开登录页
+2. 输入账号、密码
+3. 点击登录
+4.点击刷新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>页面清空所有信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 打开登录页
+2. 输入账号、密码
+3. 点击登录
+4.点击后退</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 打开登录页
+2.点击后退
+3.点击前进
+4. 输入账号、密码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>账号：ad min
+密码：admin123</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>failed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.打开页面
+2.输入账号密码
+3.点击登录
+4.再创建个新页面重复一次登录
+5.再在新页面注销登录
+6.刷新两个页面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刷新页面后登录，账号错误</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>login-042</t>
   </si>
 </sst>
 </file>
@@ -1687,7 +1677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1703,7 +1693,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -1747,7 +1737,7 @@
         <v>19</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>18</v>
@@ -1763,7 +1753,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>12</v>
@@ -1772,10 +1762,10 @@
         <v>19</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>17</v>
@@ -1788,22 +1778,22 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -1813,7 +1803,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>13</v>
@@ -1822,13 +1812,13 @@
         <v>21</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>25</v>
+        <v>256</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="I5" s="2"/>
     </row>
@@ -1838,22 +1828,22 @@
         <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>86</v>
+        <v>257</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="I6" s="2"/>
     </row>
@@ -1863,22 +1853,22 @@
         <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>90</v>
+        <v>258</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="I7" s="2"/>
     </row>
@@ -1888,22 +1878,22 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>94</v>
+        <v>260</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="I8" s="2"/>
     </row>
@@ -1913,22 +1903,22 @@
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>95</v>
+        <v>261</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="I9" s="2"/>
     </row>
@@ -1938,22 +1928,22 @@
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>31</v>
+        <v>262</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I10" s="2"/>
     </row>
@@ -1966,19 +1956,19 @@
         <v>20</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>26</v>
+        <v>263</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I11" s="3"/>
     </row>
@@ -1988,22 +1978,22 @@
         <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3"/>
     </row>
@@ -2013,22 +2003,22 @@
         <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="I13" s="3"/>
     </row>
@@ -2038,22 +2028,22 @@
         <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I14" s="3"/>
     </row>
@@ -2063,22 +2053,22 @@
         <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3"/>
     </row>
@@ -2088,22 +2078,22 @@
         <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3"/>
     </row>
@@ -2113,22 +2103,22 @@
         <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I17" s="3"/>
     </row>
@@ -2138,22 +2128,22 @@
         <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I18" s="3"/>
     </row>
@@ -2163,24 +2153,23 @@
         <v>8</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I19" s="3"/>
+        <v>93</v>
+      </c>
     </row>
     <row r="20" spans="1:9" ht="42" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
@@ -2188,22 +2177,22 @@
         <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="I20" s="2"/>
     </row>
@@ -2213,22 +2202,22 @@
         <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="I21" s="2"/>
     </row>
@@ -2238,22 +2227,22 @@
         <v>8</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="I22" s="2"/>
     </row>
@@ -2263,22 +2252,22 @@
         <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="I23" s="2"/>
     </row>
@@ -2288,22 +2277,22 @@
         <v>8</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I24" s="2"/>
     </row>
@@ -2313,10 +2302,10 @@
         <v>8</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>21</v>
@@ -2325,10 +2314,10 @@
         <v>14</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="I25" s="2"/>
     </row>
@@ -2338,22 +2327,22 @@
         <v>8</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>14</v>
+        <v>264</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="I26" s="2"/>
     </row>
@@ -2363,19 +2352,19 @@
         <v>8</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>16</v>
@@ -2388,22 +2377,22 @@
         <v>8</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="I28" s="2"/>
     </row>
@@ -2413,22 +2402,22 @@
         <v>8</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>14</v>
+        <v>264</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>128</v>
+        <v>265</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="56" x14ac:dyDescent="0.3">
@@ -2437,22 +2426,22 @@
         <v>8</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>84</v>
+        <v>264</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>129</v>
+        <v>266</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="I30" s="2"/>
     </row>
@@ -2462,819 +2451,848 @@
         <v>8</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="I31" s="2"/>
     </row>
-    <row r="32" spans="1:9" ht="98" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="84" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>142</v>
+        <v>269</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I32" s="2"/>
     </row>
-    <row r="33" spans="1:9" ht="98" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="84" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
       <c r="B33" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>150</v>
+        <v>268</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="I33" s="2"/>
     </row>
     <row r="34" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="B34" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>138</v>
+        <v>277</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>147</v>
+        <v>255</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>148</v>
+        <v>267</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I34" s="2"/>
     </row>
     <row r="35" spans="1:9" ht="42" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
       <c r="B35" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="H35" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="I35" s="2"/>
     </row>
     <row r="36" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
       <c r="B36" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>147</v>
+        <v>255</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>158</v>
+        <v>270</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>160</v>
+        <v>271</v>
       </c>
       <c r="I36" s="2"/>
     </row>
     <row r="37" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>141</v>
+        <v>264</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>158</v>
+        <v>270</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="I37" s="2"/>
     </row>
     <row r="38" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
       <c r="B38" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>141</v>
+        <v>29</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>166</v>
+        <v>272</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="I38" s="2"/>
     </row>
     <row r="39" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
       <c r="B39" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>141</v>
+        <v>29</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>173</v>
+        <v>273</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="I39" s="2"/>
     </row>
     <row r="40" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
       <c r="B40" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>147</v>
+        <v>274</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>173</v>
+        <v>273</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="I40" s="2"/>
     </row>
     <row r="41" spans="1:9" ht="42" x14ac:dyDescent="0.3">
       <c r="A41" s="2"/>
       <c r="B41" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I41" s="2"/>
+        <v>122</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="42" spans="1:9" ht="84" x14ac:dyDescent="0.3">
       <c r="A42" s="2"/>
       <c r="B42" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>141</v>
+        <v>264</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>182</v>
+        <v>276</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="I42" s="2"/>
     </row>
-    <row r="43" spans="1:9" ht="56" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" ht="42" x14ac:dyDescent="0.3">
       <c r="A43" s="2"/>
       <c r="B43" s="2" t="s">
-        <v>184</v>
+        <v>8</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>189</v>
+        <v>82</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>187</v>
+        <v>278</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>188</v>
+        <v>258</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="I43" s="2"/>
-    </row>
-    <row r="44" spans="1:9" ht="168" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A44" s="2"/>
       <c r="B44" s="2" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>233</v>
+        <v>168</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>232</v>
+        <v>164</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>239</v>
+        <v>213</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="I44" s="2"/>
     </row>
-    <row r="45" spans="1:9" ht="70" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="168" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
       <c r="B45" s="2" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>241</v>
+        <v>216</v>
       </c>
       <c r="I45" s="2"/>
     </row>
-    <row r="46" spans="1:9" ht="56" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="70" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
       <c r="B46" s="2" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>242</v>
+        <v>169</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>244</v>
+        <v>219</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="I46" s="2"/>
     </row>
-    <row r="47" spans="1:9" ht="84" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="2" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>246</v>
+        <v>164</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>247</v>
+        <v>220</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>248</v>
+        <v>221</v>
       </c>
       <c r="I47" s="2"/>
     </row>
-    <row r="48" spans="1:9" ht="98" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="84" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="2" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>216</v>
+        <v>191</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>249</v>
+        <v>218</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>266</v>
+        <v>224</v>
       </c>
       <c r="I48" s="2"/>
     </row>
     <row r="49" spans="1:9" ht="98" x14ac:dyDescent="0.3">
       <c r="A49" s="2"/>
       <c r="B49" s="2" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>250</v>
+        <v>226</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="I49" s="2"/>
     </row>
-    <row r="50" spans="1:9" ht="56" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" ht="98" x14ac:dyDescent="0.3">
       <c r="A50" s="2"/>
       <c r="B50" s="2" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>199</v>
+        <v>174</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>252</v>
+        <v>227</v>
       </c>
       <c r="I50" s="2"/>
     </row>
     <row r="51" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A51" s="2"/>
       <c r="B51" s="2" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>254</v>
+        <v>228</v>
       </c>
       <c r="I51" s="2"/>
     </row>
-    <row r="52" spans="1:9" ht="70" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A52" s="2"/>
       <c r="B52" s="2" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
       <c r="I52" s="2"/>
     </row>
     <row r="53" spans="1:9" ht="70" x14ac:dyDescent="0.3">
       <c r="A53" s="2"/>
       <c r="B53" s="2" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>257</v>
+        <v>231</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="I53" s="2"/>
     </row>
     <row r="54" spans="1:9" ht="70" x14ac:dyDescent="0.3">
       <c r="A54" s="2"/>
       <c r="B54" s="2" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>207</v>
+        <v>178</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>259</v>
+        <v>225</v>
       </c>
       <c r="F54" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="H54" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>260</v>
       </c>
       <c r="I54" s="2"/>
     </row>
     <row r="55" spans="1:9" ht="70" x14ac:dyDescent="0.3">
       <c r="A55" s="2"/>
       <c r="B55" s="2" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>259</v>
+        <v>235</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>261</v>
+        <v>237</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>262</v>
+        <v>236</v>
       </c>
       <c r="I55" s="2"/>
     </row>
     <row r="56" spans="1:9" ht="70" x14ac:dyDescent="0.3">
       <c r="A56" s="2"/>
       <c r="B56" s="2" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>224</v>
+        <v>199</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>259</v>
+        <v>235</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="I56" s="2"/>
     </row>
-    <row r="57" spans="1:9" ht="112" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" ht="70" x14ac:dyDescent="0.3">
       <c r="A57" s="2"/>
       <c r="B57" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>210</v>
-      </c>
       <c r="D57" s="2" t="s">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>259</v>
+        <v>235</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>235</v>
+        <v>155</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>268</v>
+        <v>240</v>
       </c>
       <c r="I57" s="2"/>
     </row>
     <row r="58" spans="1:9" ht="112" x14ac:dyDescent="0.3">
       <c r="A58" s="2"/>
       <c r="B58" s="2" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="C58" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="F58" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="D58" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="F58" s="2" t="s">
+      <c r="G58" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="I58" s="2"/>
+    </row>
+    <row r="59" spans="1:9" ht="112" x14ac:dyDescent="0.3">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="G58" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="I58" s="2"/>
-    </row>
-    <row r="59" spans="1:9" ht="70" x14ac:dyDescent="0.3">
-      <c r="A59" s="1"/>
-      <c r="B59" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C59" s="1" t="s">
+      <c r="F59" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="I59" s="2"/>
+    </row>
+    <row r="60" spans="1:9" ht="70" x14ac:dyDescent="0.3">
+      <c r="A60" s="1"/>
+      <c r="B60" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="D59" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="I59" s="1"/>
-    </row>
-    <row r="60" spans="1:9" ht="56" x14ac:dyDescent="0.3">
-      <c r="A60" s="1"/>
-      <c r="B60" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>178</v>
-      </c>
       <c r="G60" s="2" t="s">
-        <v>272</v>
+        <v>246</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>273</v>
+        <v>247</v>
       </c>
       <c r="I60" s="1"/>
     </row>
-    <row r="61" spans="1:9" ht="98" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="1" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>259</v>
+        <v>235</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>275</v>
+        <v>248</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>249</v>
       </c>
       <c r="I61" s="1"/>
     </row>
-    <row r="62" spans="1:9" ht="56" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" ht="98" x14ac:dyDescent="0.3">
+      <c r="A62" s="1"/>
       <c r="B62" s="1" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>259</v>
+        <v>235</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>276</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="I62" s="1"/>
     </row>
     <row r="63" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>231</v>
+        <v>206</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>277</v>
+        <v>248</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>278</v>
+        <v>252</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="56" x14ac:dyDescent="0.3">
+      <c r="B64" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>254</v>
       </c>
     </row>
   </sheetData>

--- a/测试用例.xlsx
+++ b/测试用例.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\programming\bear\pht\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E9AA73A-FC2B-4C0A-B5AF-72A6C7A158A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4029BC16-0C81-4AE9-99C9-833A3008138A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30072" yWindow="5400" windowWidth="20868" windowHeight="14472" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="274">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -569,12 +569,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1.验证码图片更新
-2.输入框均为空
-3.验证码uuid更新</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>登录</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -649,17 +643,7 @@
     <t>login-035</t>
   </si>
   <si>
-    <t>登录成功后刷新</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>login-036</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.跳转页面到若衣管理系统
-2.账号名是admin
-3.刷新后仍是若衣管理系统</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -833,10 +817,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>修改指定用户，界面生效</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>修改指定用户界面，点击取消</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -894,9 +874,6 @@
   </si>
   <si>
     <t>alter-005</t>
-  </si>
-  <si>
-    <t>alter-006</t>
   </si>
   <si>
     <t>del-001</t>
@@ -1091,10 +1068,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>网页端界面普通人ptr变成普通人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1.登录到首页
 2.进入到用户管理，点击普通人ptr用户的选择框
 3.点击修改
@@ -1151,19 +1124,9 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>网页端显示部门下有该用户
-数据库查询该用户有对应depid</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1.登录到首页
 2.进入到用户管理，点击普通人ptr用户的选择框
 3.点击删除，再确定</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据库查询该用户被删除
-表格消失显示该用户</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1340,7 +1303,24 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>login-042</t>
+    <t xml:space="preserve">1.验证码图片更新
+2.输入框均为空
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.验证码图片更新
+2.输入框均为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>显示该用户有部门</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库查询该用户没被删除
+表格消失显示该用户</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1677,7 +1657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1787,7 +1767,7 @@
         <v>116</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>85</v>
@@ -1812,7 +1792,7 @@
         <v>21</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>100</v>
@@ -1837,7 +1817,7 @@
         <v>21</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>85</v>
@@ -1862,7 +1842,7 @@
         <v>21</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>85</v>
@@ -1887,7 +1867,7 @@
         <v>116</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>85</v>
@@ -1912,7 +1892,7 @@
         <v>116</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>85</v>
@@ -1937,7 +1917,7 @@
         <v>21</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>99</v>
@@ -1962,7 +1942,7 @@
         <v>116</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>85</v>
@@ -2034,7 +2014,7 @@
         <v>61</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>86</v>
@@ -2059,7 +2039,7 @@
         <v>62</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
@@ -2084,7 +2064,7 @@
         <v>63</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>88</v>
@@ -2109,7 +2089,7 @@
         <v>64</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>89</v>
@@ -2134,7 +2114,7 @@
         <v>65</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
@@ -2289,7 +2269,7 @@
         <v>104</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>32</v>
@@ -2336,7 +2316,7 @@
         <v>21</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>107</v>
@@ -2358,7 +2338,7 @@
         <v>74</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>109</v>
@@ -2408,13 +2388,13 @@
         <v>76</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>113</v>
@@ -2432,13 +2412,13 @@
         <v>77</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>115</v>
@@ -2466,29 +2446,29 @@
         <v>121</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>122</v>
+        <v>270</v>
       </c>
       <c r="I31" s="2"/>
     </row>
     <row r="32" spans="1:9" ht="84" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>104</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>32</v>
@@ -2498,47 +2478,47 @@
     <row r="33" spans="1:9" ht="84" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
       <c r="B33" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="I33" s="2"/>
     </row>
     <row r="34" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="B34" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>22</v>
@@ -2548,72 +2528,72 @@
     <row r="35" spans="1:9" ht="42" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
       <c r="B35" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D35" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I35" s="2"/>
     </row>
     <row r="36" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
       <c r="B36" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C36" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="E36" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="I36" s="2"/>
     </row>
     <row r="37" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>140</v>
+        <v>122</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F37" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>270</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>142</v>
@@ -2623,473 +2603,473 @@
     <row r="38" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
       <c r="B38" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>144</v>
+        <v>122</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I38" s="2"/>
     </row>
     <row r="39" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
       <c r="B39" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>29</v>
+        <v>266</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>151</v>
+        <v>243</v>
       </c>
       <c r="I39" s="2"/>
     </row>
-    <row r="40" spans="1:9" ht="56" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="42" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
       <c r="B40" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>274</v>
-      </c>
       <c r="G40" s="2" t="s">
-        <v>273</v>
+        <v>153</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="I40" s="2"/>
-    </row>
-    <row r="41" spans="1:9" ht="42" x14ac:dyDescent="0.3">
+        <v>271</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="84" x14ac:dyDescent="0.3">
       <c r="A41" s="2"/>
       <c r="B41" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C41" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>149</v>
-      </c>
       <c r="E41" s="2" t="s">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>155</v>
+        <v>256</v>
       </c>
       <c r="G41" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="H41" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="H41" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="84" x14ac:dyDescent="0.3">
+      <c r="I41" s="2"/>
+    </row>
+    <row r="42" spans="1:9" ht="42" x14ac:dyDescent="0.3">
       <c r="A42" s="2"/>
       <c r="B42" s="2" t="s">
-        <v>123</v>
+        <v>8</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>276</v>
+        <v>251</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I42" s="2"/>
-    </row>
-    <row r="43" spans="1:9" ht="42" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A43" s="2"/>
       <c r="B43" s="2" t="s">
-        <v>8</v>
+        <v>157</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>82</v>
+        <v>162</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>278</v>
+        <v>160</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>258</v>
+        <v>161</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>259</v>
+        <v>208</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="56" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+      <c r="I43" s="2"/>
+    </row>
+    <row r="44" spans="1:9" ht="168" x14ac:dyDescent="0.3">
       <c r="A44" s="2"/>
       <c r="B44" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I44" s="2"/>
     </row>
-    <row r="45" spans="1:9" ht="168" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="70" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
       <c r="B45" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C45" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>209</v>
-      </c>
       <c r="F45" s="2" t="s">
-        <v>208</v>
+        <v>161</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="I45" s="2"/>
     </row>
-    <row r="46" spans="1:9" ht="70" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
       <c r="B46" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>169</v>
+        <v>213</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I46" s="2"/>
     </row>
-    <row r="47" spans="1:9" ht="56" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="84" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E47" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G47" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="F47" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="H47" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I47" s="2"/>
     </row>
-    <row r="48" spans="1:9" ht="84" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="98" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>222</v>
+        <v>161</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="I48" s="2"/>
     </row>
     <row r="49" spans="1:9" ht="98" x14ac:dyDescent="0.3">
       <c r="A49" s="2"/>
       <c r="B49" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="I49" s="2"/>
     </row>
-    <row r="50" spans="1:9" ht="98" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A50" s="2"/>
       <c r="B50" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I50" s="2"/>
     </row>
     <row r="51" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A51" s="2"/>
       <c r="B51" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E51" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="H51" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F51" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>228</v>
-      </c>
       <c r="I51" s="2"/>
     </row>
-    <row r="52" spans="1:9" ht="56" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" ht="70" x14ac:dyDescent="0.3">
       <c r="A52" s="2"/>
       <c r="B52" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I52" s="2"/>
     </row>
     <row r="53" spans="1:9" ht="70" x14ac:dyDescent="0.3">
       <c r="A53" s="2"/>
       <c r="B53" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I53" s="2"/>
     </row>
     <row r="54" spans="1:9" ht="70" x14ac:dyDescent="0.3">
       <c r="A54" s="2"/>
       <c r="B54" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>164</v>
+        <v>205</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="I54" s="2"/>
     </row>
     <row r="55" spans="1:9" ht="70" x14ac:dyDescent="0.3">
       <c r="A55" s="2"/>
       <c r="B55" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>210</v>
+        <v>152</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I55" s="2"/>
     </row>
-    <row r="56" spans="1:9" ht="70" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" ht="112" x14ac:dyDescent="0.3">
       <c r="A56" s="2"/>
       <c r="B56" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>237</v>
@@ -3099,200 +3079,150 @@
       </c>
       <c r="I56" s="2"/>
     </row>
-    <row r="57" spans="1:9" ht="70" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" ht="112" x14ac:dyDescent="0.3">
       <c r="A57" s="2"/>
       <c r="B57" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E57" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="G57" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="F57" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G57" s="2" t="s">
+      <c r="H57" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="H57" s="2" t="s">
+      <c r="I57" s="2"/>
+    </row>
+    <row r="58" spans="1:9" ht="70" x14ac:dyDescent="0.3">
+      <c r="A58" s="1"/>
+      <c r="B58" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="G58" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="I57" s="2"/>
-    </row>
-    <row r="58" spans="1:9" ht="112" x14ac:dyDescent="0.3">
-      <c r="A58" s="2"/>
-      <c r="B58" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>243</v>
-      </c>
       <c r="H58" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="I58" s="2"/>
-    </row>
-    <row r="59" spans="1:9" ht="112" x14ac:dyDescent="0.3">
-      <c r="A59" s="2"/>
-      <c r="B59" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>202</v>
+        <v>272</v>
+      </c>
+      <c r="I58" s="1"/>
+    </row>
+    <row r="59" spans="1:9" ht="56" x14ac:dyDescent="0.3">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>199</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>211</v>
+        <v>230</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>152</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>241</v>
       </c>
       <c r="H59" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="I59" s="1"/>
+    </row>
+    <row r="60" spans="1:9" ht="98" x14ac:dyDescent="0.3">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="I60" s="1"/>
+    </row>
+    <row r="61" spans="1:9" ht="56" x14ac:dyDescent="0.3">
+      <c r="B61" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="56" x14ac:dyDescent="0.3">
+      <c r="B62" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G62" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="I59" s="2"/>
-    </row>
-    <row r="60" spans="1:9" ht="70" x14ac:dyDescent="0.3">
-      <c r="A60" s="1"/>
-      <c r="B60" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="G60" s="2" t="s">
+      <c r="H62" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="I60" s="1"/>
-    </row>
-    <row r="61" spans="1:9" ht="56" x14ac:dyDescent="0.3">
-      <c r="A61" s="1"/>
-      <c r="B61" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="I61" s="1"/>
-    </row>
-    <row r="62" spans="1:9" ht="98" x14ac:dyDescent="0.3">
-      <c r="A62" s="1"/>
-      <c r="B62" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="I62" s="1"/>
-    </row>
-    <row r="63" spans="1:9" ht="56" x14ac:dyDescent="0.3">
-      <c r="B63" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ht="56" x14ac:dyDescent="0.3">
-      <c r="B64" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>254</v>
       </c>
     </row>
   </sheetData>
